--- a/docs/reports/daily/WCR_Kavach_Unified_KPI_Jun30-Jun30.xlsx
+++ b/docs/reports/daily/WCR_Kavach_Unified_KPI_Jun30-Jun30.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,10 +22,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="#,##0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -185,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -207,13 +207,13 @@
     <xf numFmtId="3" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -229,7 +229,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -244,7 +244,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -259,7 +259,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -309,6 +309,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -714,7 +732,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -857,19 +874,19 @@
         <f>'Daily Breakdown'!J37</f>
         <v/>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="46">
         <f>IFERROR(G5/D5,0)</f>
         <v/>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="47">
         <f>IFERROR(G5/E5,0)</f>
         <v/>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="48">
         <f>IFERROR(G5/E5*100,0)</f>
         <v/>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="47">
         <f>IFERROR(G5/(D5*E5/1000),0)</f>
         <v/>
       </c>
@@ -877,19 +894,19 @@
         <f>'Daily Breakdown'!K37</f>
         <v/>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="46">
         <f>IFERROR(N5/D5,0)</f>
         <v/>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="47">
         <f>IFERROR(N5/E5,0)</f>
         <v/>
       </c>
-      <c r="Q5" s="10">
+      <c r="Q5" s="47">
         <f>IFERROR(N5/(D5*E5/100),0)</f>
         <v/>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="48">
         <f>IFERROR(N5/E5*100,0)</f>
         <v/>
       </c>
@@ -939,7 +956,13 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="37" t="inlineStr">
+        <is>
+          <t>Availability base excludes locos with FS+OS pkts = 0 (they are still listed below; only the Total-pkts availability base drops them).</t>
+        </is>
+      </c>
+    </row>
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -1011,7 +1034,7 @@
       <c r="C4" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="49" t="n">
         <v>543.89</v>
       </c>
       <c r="E4" s="18" t="n">
@@ -1051,7 +1074,7 @@
       <c r="C5" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="49" t="n">
         <v>541.6</v>
       </c>
       <c r="E5" s="18" t="n">
@@ -1091,7 +1114,7 @@
       <c r="C6" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="49" t="n">
         <v>541.97</v>
       </c>
       <c r="E6" s="18" t="n">
@@ -1131,7 +1154,7 @@
       <c r="C7" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="49" t="n">
         <v>541.51</v>
       </c>
       <c r="E7" s="18" t="n">
@@ -1171,7 +1194,7 @@
       <c r="C8" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="49" t="n">
         <v>536.3</v>
       </c>
       <c r="E8" s="18" t="n">
@@ -1211,7 +1234,7 @@
       <c r="C9" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="49" t="n">
         <v>251.85</v>
       </c>
       <c r="E9" s="18" t="n">
@@ -1251,7 +1274,7 @@
       <c r="C10" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="49" t="n">
         <v>512.54</v>
       </c>
       <c r="E10" s="18" t="n">
@@ -1291,7 +1314,7 @@
       <c r="C11" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="49" t="n">
         <v>329.85</v>
       </c>
       <c r="E11" s="18" t="n">
@@ -1331,7 +1354,7 @@
       <c r="C12" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="49" t="n">
         <v>470.59</v>
       </c>
       <c r="E12" s="18" t="n">
@@ -1371,7 +1394,7 @@
       <c r="C13" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="49" t="n">
         <v>453.19</v>
       </c>
       <c r="E13" s="18" t="n">
@@ -1411,7 +1434,7 @@
       <c r="C14" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="49" t="n">
         <v>250.87</v>
       </c>
       <c r="E14" s="18" t="n">
@@ -1451,7 +1474,7 @@
       <c r="C15" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="49" t="n">
         <v>291.96</v>
       </c>
       <c r="E15" s="18" t="n">
@@ -1491,7 +1514,7 @@
       <c r="C16" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="49" t="n">
         <v>322.61</v>
       </c>
       <c r="E16" s="18" t="n">
@@ -1531,7 +1554,7 @@
       <c r="C17" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="49" t="n">
         <v>322.6</v>
       </c>
       <c r="E17" s="18" t="n">
@@ -1571,7 +1594,7 @@
       <c r="C18" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="49" t="n">
         <v>188.65</v>
       </c>
       <c r="E18" s="18" t="n">
@@ -1611,7 +1634,7 @@
       <c r="C19" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="49" t="n">
         <v>218.84</v>
       </c>
       <c r="E19" s="18" t="n">
@@ -1651,7 +1674,7 @@
       <c r="C20" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="49" t="n">
         <v>273</v>
       </c>
       <c r="E20" s="18" t="n">
@@ -1691,7 +1714,7 @@
       <c r="C21" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="49" t="n">
         <v>321.47</v>
       </c>
       <c r="E21" s="18" t="n">
@@ -1731,7 +1754,7 @@
       <c r="C22" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="49" t="n">
         <v>109.22</v>
       </c>
       <c r="E22" s="18" t="n">
@@ -1771,7 +1794,7 @@
       <c r="C23" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="49" t="n">
         <v>320.2</v>
       </c>
       <c r="E23" s="18" t="n">
@@ -1811,7 +1834,7 @@
       <c r="C24" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="49" t="n">
         <v>319.23</v>
       </c>
       <c r="E24" s="18" t="n">
@@ -1851,7 +1874,7 @@
       <c r="C25" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="49" t="n">
         <v>150.95</v>
       </c>
       <c r="E25" s="18" t="n">
@@ -1891,7 +1914,7 @@
       <c r="C26" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="49" t="n">
         <v>108.66</v>
       </c>
       <c r="E26" s="18" t="n">
@@ -1931,7 +1954,7 @@
       <c r="C27" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="49" t="n">
         <v>248.23</v>
       </c>
       <c r="E27" s="18" t="n">
@@ -1971,7 +1994,7 @@
       <c r="C28" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="49" t="n">
         <v>108.54</v>
       </c>
       <c r="E28" s="18" t="n">
@@ -2011,7 +2034,7 @@
       <c r="C29" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D29" s="49" t="n">
         <v>318.76</v>
       </c>
       <c r="E29" s="18" t="n">
@@ -2051,7 +2074,7 @@
       <c r="C30" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="49" t="n">
         <v>220.27</v>
       </c>
       <c r="E30" s="18" t="n">
@@ -2091,7 +2114,7 @@
       <c r="C31" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D31" s="49" t="n">
         <v>181.09</v>
       </c>
       <c r="E31" s="18" t="n">
@@ -2131,7 +2154,7 @@
       <c r="C32" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="17" t="n">
+      <c r="D32" s="49" t="n">
         <v>59.83</v>
       </c>
       <c r="E32" s="18" t="n">
@@ -2171,7 +2194,7 @@
       <c r="C33" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="17" t="n">
+      <c r="D33" s="49" t="n">
         <v>88.42</v>
       </c>
       <c r="E33" s="18" t="n">
@@ -2211,7 +2234,7 @@
       <c r="C34" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D34" s="17" t="n">
+      <c r="D34" s="49" t="n">
         <v>9.91</v>
       </c>
       <c r="E34" s="18" t="n">
@@ -2251,7 +2274,7 @@
       <c r="C35" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D35" s="17" t="n">
+      <c r="D35" s="49" t="n">
         <v>0.36</v>
       </c>
       <c r="E35" s="18" t="n">
@@ -2292,7 +2315,7 @@
         <f>SUM(C4:C35)</f>
         <v/>
       </c>
-      <c r="D36" s="22">
+      <c r="D36" s="50">
         <f>SUM(D4:D35)</f>
         <v/>
       </c>
@@ -2301,7 +2324,7 @@
         <v/>
       </c>
       <c r="F36" s="23">
-        <f>SUM(F4:F35)</f>
+        <f>SUMIF(E4:E35,"&gt;0",F4:F35)</f>
         <v/>
       </c>
       <c r="G36" s="24">
@@ -2336,7 +2359,7 @@
         <f>C36</f>
         <v/>
       </c>
-      <c r="D37" s="27">
+      <c r="D37" s="51">
         <f>D36</f>
         <v/>
       </c>
@@ -2414,7 +2437,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="30" t="inlineStr">
         <is>
@@ -2422,7 +2444,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
@@ -6424,7 +6445,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -9440,7 +9460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="B1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -9455,7 +9475,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="34" customHeight="1">
       <c r="B3" s="44" t="inlineStr">
         <is>

--- a/docs/reports/daily/WCR_Kavach_Unified_KPI_Jun30-Jun30.xlsx
+++ b/docs/reports/daily/WCR_Kavach_Unified_KPI_Jun30-Jun30.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2735,7 +2735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L69"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2813,6 +2813,11 @@
           <t>Valid Trip?</t>
         </is>
       </c>
+      <c r="M5" s="14" t="inlineStr">
+        <is>
+          <t>Loco Travel</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="34" t="inlineStr">
@@ -2869,6 +2874,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M6" s="16" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="34" t="inlineStr">
@@ -2925,6 +2931,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M7" s="16" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="34" t="inlineStr">
@@ -2981,6 +2988,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M8" s="16" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
@@ -3037,6 +3045,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M9" s="16" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
@@ -3093,6 +3102,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M10" s="16" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="34" t="inlineStr">
@@ -3149,6 +3159,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M11" s="16" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="34" t="inlineStr">
@@ -3205,6 +3216,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M12" s="16" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="34" t="inlineStr">
@@ -3261,6 +3273,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M13" s="16" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="34" t="inlineStr">
@@ -3317,6 +3330,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M14" s="16" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="34" t="inlineStr">
@@ -3373,6 +3387,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M15" s="16" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="34" t="inlineStr">
@@ -3429,6 +3444,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M16" s="16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="34" t="inlineStr">
@@ -3485,6 +3501,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M17" s="16" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="34" t="inlineStr">
@@ -3541,6 +3558,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M18" s="16" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="34" t="inlineStr">
@@ -3597,6 +3615,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M19" s="16" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="34" t="inlineStr">
@@ -3653,6 +3672,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M20" s="16" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="34" t="inlineStr">
@@ -3709,6 +3729,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M21" s="16" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="34" t="inlineStr">
@@ -3765,6 +3786,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M22" s="16" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="34" t="inlineStr">
@@ -3821,6 +3843,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M23" s="16" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="34" t="inlineStr">
@@ -3877,6 +3900,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M24" s="16" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="34" t="inlineStr">
@@ -3933,6 +3957,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M25" s="16" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="34" t="inlineStr">
@@ -3989,6 +4014,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M26" s="16" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="34" t="inlineStr">
@@ -4045,6 +4071,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M27" s="16" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="34" t="inlineStr">
@@ -4101,6 +4128,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M28" s="16" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="34" t="inlineStr">
@@ -4157,6 +4185,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M29" s="16" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="34" t="inlineStr">
@@ -4213,6 +4242,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M30" s="16" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="34" t="inlineStr">
@@ -4269,6 +4299,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M31" s="16" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="34" t="inlineStr">
@@ -4325,6 +4356,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M32" s="16" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
@@ -4381,6 +4413,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M33" s="16" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="34" t="inlineStr">
@@ -4437,6 +4470,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M34" s="16" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
@@ -4493,6 +4527,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M35" s="16" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
@@ -4549,6 +4584,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M36" s="16" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
@@ -4605,6 +4641,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M37" s="16" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
@@ -4661,6 +4698,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M38" s="16" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="34" t="inlineStr">
@@ -4717,6 +4755,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M39" s="16" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="34" t="inlineStr">
@@ -4773,6 +4812,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M40" s="16" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="34" t="inlineStr">
@@ -4829,6 +4869,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M41" s="16" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="34" t="inlineStr">
@@ -4885,6 +4926,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M42" s="16" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="34" t="inlineStr">
@@ -4941,6 +4983,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M43" s="16" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="34" t="inlineStr">
@@ -4997,6 +5040,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M44" s="16" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="34" t="inlineStr">
@@ -5053,6 +5097,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M45" s="16" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
@@ -5109,6 +5154,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M46" s="16" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="34" t="inlineStr">
@@ -5165,6 +5211,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M47" s="16" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="34" t="inlineStr">
@@ -5221,6 +5268,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M48" s="16" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="34" t="inlineStr">
@@ -5277,6 +5325,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M49" s="16" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="34" t="inlineStr">
@@ -5333,6 +5382,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M50" s="16" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="34" t="inlineStr">
@@ -5389,6 +5439,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M51" s="16" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="34" t="inlineStr">
@@ -5445,6 +5496,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M52" s="16" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="34" t="inlineStr">
@@ -5501,6 +5553,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M53" s="16" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
@@ -5557,6 +5610,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M54" s="16" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="34" t="inlineStr">
@@ -5613,6 +5667,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M55" s="16" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="34" t="inlineStr">
@@ -5669,6 +5724,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M56" s="16" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="34" t="inlineStr">
@@ -5725,6 +5781,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M57" s="16" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="34" t="inlineStr">
@@ -5781,6 +5838,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M58" s="16" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="34" t="inlineStr">
@@ -5837,6 +5895,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M59" s="16" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="34" t="inlineStr">
@@ -5893,6 +5952,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M60" s="16" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="34" t="inlineStr">
@@ -5949,6 +6009,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M61" s="16" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="34" t="inlineStr">
@@ -6005,6 +6066,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M62" s="16" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="34" t="inlineStr">
@@ -6061,6 +6123,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M63" s="16" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="34" t="inlineStr">
@@ -6117,6 +6180,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M64" s="16" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="34" t="inlineStr">
@@ -6173,6 +6237,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M65" s="16" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="34" t="inlineStr">
@@ -6229,6 +6294,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M66" s="16" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="34" t="inlineStr">
@@ -6285,6 +6351,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M67" s="16" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="34" t="inlineStr">
@@ -6341,6 +6408,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M68" s="16" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="34" t="inlineStr">
@@ -6397,6 +6465,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M69" s="16" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/docs/reports/daily/WCR_Kavach_Unified_KPI_Jun30-Jun30.xlsx
+++ b/docs/reports/daily/WCR_Kavach_Unified_KPI_Jun30-Jun30.xlsx
@@ -2874,7 +2874,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M6" s="16" t="inlineStr"/>
+      <c r="M6" s="16" t="inlineStr">
+        <is>
+          <t>Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="34" t="inlineStr">
@@ -2931,7 +2935,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M7" s="16" t="inlineStr"/>
+      <c r="M7" s="16" t="inlineStr">
+        <is>
+          <t>SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="34" t="inlineStr">
@@ -2988,7 +2996,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M8" s="16" t="inlineStr"/>
+      <c r="M8" s="16" t="inlineStr">
+        <is>
+          <t>SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
@@ -3045,7 +3057,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M9" s="16" t="inlineStr"/>
+      <c r="M9" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
@@ -3102,7 +3118,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M10" s="16" t="inlineStr"/>
+      <c r="M10" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="34" t="inlineStr">
@@ -3159,7 +3179,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M11" s="16" t="inlineStr"/>
+      <c r="M11" s="16" t="inlineStr">
+        <is>
+          <t>Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="34" t="inlineStr">
@@ -3216,7 +3240,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M12" s="16" t="inlineStr"/>
+      <c r="M12" s="16" t="inlineStr">
+        <is>
+          <t>Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="34" t="inlineStr">
@@ -3273,7 +3301,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M13" s="16" t="inlineStr"/>
+      <c r="M13" s="16" t="inlineStr">
+        <is>
+          <t>KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="34" t="inlineStr">
@@ -3330,7 +3362,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M14" s="16" t="inlineStr"/>
+      <c r="M14" s="16" t="inlineStr">
+        <is>
+          <t>KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="34" t="inlineStr">
@@ -3387,7 +3423,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M15" s="16" t="inlineStr"/>
+      <c r="M15" s="16" t="inlineStr">
+        <is>
+          <t>KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="34" t="inlineStr">
@@ -3444,7 +3484,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M16" s="16" t="inlineStr"/>
+      <c r="M16" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="34" t="inlineStr">
@@ -3501,7 +3545,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M17" s="16" t="inlineStr"/>
+      <c r="M17" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="34" t="inlineStr">
@@ -3558,7 +3606,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M18" s="16" t="inlineStr"/>
+      <c r="M18" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="34" t="inlineStr">
@@ -3615,7 +3667,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M19" s="16" t="inlineStr"/>
+      <c r="M19" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="34" t="inlineStr">
@@ -3672,7 +3728,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M20" s="16" t="inlineStr"/>
+      <c r="M20" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="34" t="inlineStr">
@@ -3729,7 +3789,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M21" s="16" t="inlineStr"/>
+      <c r="M21" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="34" t="inlineStr">
@@ -3786,7 +3850,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M22" s="16" t="inlineStr"/>
+      <c r="M22" s="16" t="inlineStr">
+        <is>
+          <t>Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="34" t="inlineStr">
@@ -3843,7 +3911,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M23" s="16" t="inlineStr"/>
+      <c r="M23" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="34" t="inlineStr">
@@ -3900,7 +3972,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M24" s="16" t="inlineStr"/>
+      <c r="M24" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="34" t="inlineStr">
@@ -3957,7 +4033,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M25" s="16" t="inlineStr"/>
+      <c r="M25" s="16" t="inlineStr">
+        <is>
+          <t>Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="34" t="inlineStr">
@@ -4014,7 +4094,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M26" s="16" t="inlineStr"/>
+      <c r="M26" s="16" t="inlineStr">
+        <is>
+          <t>Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="34" t="inlineStr">
@@ -4071,7 +4155,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M27" s="16" t="inlineStr"/>
+      <c r="M27" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="34" t="inlineStr">
@@ -4128,7 +4216,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M28" s="16" t="inlineStr"/>
+      <c r="M28" s="16" t="inlineStr">
+        <is>
+          <t>Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="34" t="inlineStr">
@@ -4185,7 +4277,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M29" s="16" t="inlineStr"/>
+      <c r="M29" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="34" t="inlineStr">
@@ -4242,7 +4338,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M30" s="16" t="inlineStr"/>
+      <c r="M30" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="34" t="inlineStr">
@@ -4299,7 +4399,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M31" s="16" t="inlineStr"/>
+      <c r="M31" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="34" t="inlineStr">
@@ -4356,7 +4460,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M32" s="16" t="inlineStr"/>
+      <c r="M32" s="16" t="inlineStr">
+        <is>
+          <t>Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
@@ -4413,7 +4521,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M33" s="16" t="inlineStr"/>
+      <c r="M33" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="34" t="inlineStr">
@@ -4470,7 +4582,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M34" s="16" t="inlineStr"/>
+      <c r="M34" s="16" t="inlineStr">
+        <is>
+          <t>SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
@@ -4527,7 +4643,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M35" s="16" t="inlineStr"/>
+      <c r="M35" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
@@ -4584,7 +4704,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M36" s="16" t="inlineStr"/>
+      <c r="M36" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
@@ -4641,7 +4765,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M37" s="16" t="inlineStr"/>
+      <c r="M37" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
@@ -4698,7 +4826,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M38" s="16" t="inlineStr"/>
+      <c r="M38" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="34" t="inlineStr">
@@ -4755,7 +4887,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M39" s="16" t="inlineStr"/>
+      <c r="M39" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="34" t="inlineStr">
@@ -4812,7 +4948,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M40" s="16" t="inlineStr"/>
+      <c r="M40" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="34" t="inlineStr">
@@ -4869,7 +5009,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M41" s="16" t="inlineStr"/>
+      <c r="M41" s="16" t="inlineStr">
+        <is>
+          <t>SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="34" t="inlineStr">
@@ -4926,7 +5070,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M42" s="16" t="inlineStr"/>
+      <c r="M42" s="16" t="inlineStr">
+        <is>
+          <t>Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="34" t="inlineStr">
@@ -4983,7 +5131,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M43" s="16" t="inlineStr"/>
+      <c r="M43" s="16" t="inlineStr">
+        <is>
+          <t>SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="34" t="inlineStr">
@@ -5040,7 +5192,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M44" s="16" t="inlineStr"/>
+      <c r="M44" s="16" t="inlineStr">
+        <is>
+          <t>Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="34" t="inlineStr">
@@ -5097,7 +5253,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M45" s="16" t="inlineStr"/>
+      <c r="M45" s="16" t="inlineStr">
+        <is>
+          <t>Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
@@ -5154,7 +5314,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M46" s="16" t="inlineStr"/>
+      <c r="M46" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="34" t="inlineStr">
@@ -5211,7 +5375,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M47" s="16" t="inlineStr"/>
+      <c r="M47" s="16" t="inlineStr">
+        <is>
+          <t>Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="34" t="inlineStr">
@@ -5268,7 +5436,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M48" s="16" t="inlineStr"/>
+      <c r="M48" s="16" t="inlineStr">
+        <is>
+          <t>Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="34" t="inlineStr">
@@ -5325,7 +5497,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M49" s="16" t="inlineStr"/>
+      <c r="M49" s="16" t="inlineStr">
+        <is>
+          <t>Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="34" t="inlineStr">
@@ -5382,7 +5558,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M50" s="16" t="inlineStr"/>
+      <c r="M50" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="34" t="inlineStr">
@@ -5439,7 +5619,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M51" s="16" t="inlineStr"/>
+      <c r="M51" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="34" t="inlineStr">
@@ -5496,7 +5680,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M52" s="16" t="inlineStr"/>
+      <c r="M52" s="16" t="inlineStr">
+        <is>
+          <t>Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="34" t="inlineStr">
@@ -5553,7 +5741,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M53" s="16" t="inlineStr"/>
+      <c r="M53" s="16" t="inlineStr">
+        <is>
+          <t>Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
@@ -5610,7 +5802,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M54" s="16" t="inlineStr"/>
+      <c r="M54" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="34" t="inlineStr">
@@ -5667,7 +5863,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M55" s="16" t="inlineStr"/>
+      <c r="M55" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="34" t="inlineStr">
@@ -5724,7 +5924,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M56" s="16" t="inlineStr"/>
+      <c r="M56" s="16" t="inlineStr">
+        <is>
+          <t>SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="34" t="inlineStr">
@@ -5781,7 +5985,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M57" s="16" t="inlineStr"/>
+      <c r="M57" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="34" t="inlineStr">
@@ -5838,7 +6046,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M58" s="16" t="inlineStr"/>
+      <c r="M58" s="16" t="inlineStr">
+        <is>
+          <t>Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="34" t="inlineStr">
@@ -5895,7 +6107,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M59" s="16" t="inlineStr"/>
+      <c r="M59" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="34" t="inlineStr">
@@ -5952,7 +6168,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M60" s="16" t="inlineStr"/>
+      <c r="M60" s="16" t="inlineStr">
+        <is>
+          <t>IBH 265, Murhesi Rampur(MSRP), IBH/LC-258, Jajjanpatti(JJA), DhaurmuiJaghina(DUM), IBH-247, Bharatpur Jn.(BTE), IBH-242, Sewar(SWAR), IBH-JCU, LC-232, Pingora(PNGR), IBH-229, 2.35 KM from KEV, Kela Devi(KEV), IBH-224, Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="34" t="inlineStr">
@@ -6009,7 +6229,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M61" s="16" t="inlineStr"/>
+      <c r="M61" s="16" t="inlineStr">
+        <is>
+          <t>SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="34" t="inlineStr">
@@ -6066,7 +6290,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M62" s="16" t="inlineStr"/>
+      <c r="M62" s="16" t="inlineStr">
+        <is>
+          <t>Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="34" t="inlineStr">
@@ -6123,7 +6351,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M63" s="16" t="inlineStr"/>
+      <c r="M63" s="16" t="inlineStr">
+        <is>
+          <t>Bayana Jn.(BXN), LC-219, LC-217, IBH-216, Dumariya(DY), IBH-211, FatehSinghpura(FSP), IBH-DNHK, Hindaun City(HAN), LC-199, IBS-198, Shri Mahabirji(SMBJ), IBH-192, Piloda(PDZ), ChhotiOdai(COO), 8.375 KM from GGC, IBH-180, Gangapur City(GGC), Lalpur Umri(LRU), IBH/LC-173, NarayanpurTatwara(NNW), IBH-171, Nimoda(NMD), 3.5 KM from MLZ, Malarna(MLZ), IBH-MXL, LC-163, Makholi(MXL), IBH-159, Ranthambhor(RNT), 5.0 KM from SWM-A, SawaiMadhopurJn(SWM), LC-148, Kushtala(KTA), IBH-RWJ, 2.0 KM from RWJ, RawanjnaDungar(RWJ), 6.25 KM from AMLI, Amli(AMLI), IBH-140, IndragarhSumerganjMandi(IDG), LC-137, IBH-LKE, Lakheri(LKE), LC-136W, Laban(LBN), IBH-LBN, Ghatkavarana(GKB), IBH-131, LC-128, Kapren(KPZ), LC-126, IBH-125, Arnetha(ARE), LC-120, IBH-119, LC-118, KeshoraiPatan(KPTN), 2.75 KM from GQL (LC-113), Gurla(GQL), KOTA C, Kota Jn.(KOTA) CENTRAL</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="34" t="inlineStr">
@@ -6180,7 +6412,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M64" s="16" t="inlineStr"/>
+      <c r="M64" s="16" t="inlineStr">
+        <is>
+          <t>Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="34" t="inlineStr">
@@ -6237,7 +6473,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M65" s="16" t="inlineStr"/>
+      <c r="M65" s="16" t="inlineStr">
+        <is>
+          <t>Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="34" t="inlineStr">
@@ -6294,7 +6534,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M66" s="16" t="inlineStr"/>
+      <c r="M66" s="16" t="inlineStr">
+        <is>
+          <t>Kota Jn.(KOTA) CENTRAL, KOTA SOUTH, DakaniyaTalav(DKNT), Dadhdevi(DDV), ALNI/DDV, Alniya(ALNI), IBH DHANIKASAR, Ravtha Road(RDT), IBH-95(7.25KM FROM DARA), Dara(DARA), IBH KIW-DARA, Kanwalpura(KIW), 2.85 KM from MKX, Morak(MKX), IBH RMA-MKX, RamganjMandi(RMA), IBH-79, Jhalawar Road(JHW), DhuanKheri(DKRA), IBH-69, Bhawani Mandi(BWM), IBH-61(LC-60), Kurlasi(KRLS), IBH-55(7.5KM from GOH), Garoth(GOH), IBH-48, Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="34" t="inlineStr">
@@ -6351,7 +6595,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M67" s="16" t="inlineStr"/>
+      <c r="M67" s="16" t="inlineStr">
+        <is>
+          <t>Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="34" t="inlineStr">
@@ -6408,7 +6656,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M68" s="16" t="inlineStr"/>
+      <c r="M68" s="16" t="inlineStr">
+        <is>
+          <t>Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="34" t="inlineStr">
@@ -6465,7 +6717,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M69" s="16" t="inlineStr"/>
+      <c r="M69" s="16" t="inlineStr">
+        <is>
+          <t>Shamgarh(SGZ), 3.0 Km From SGZ, IBH-HNU, Suwasra(SVA), NathuKheri(NKH), 4.5 KM from CMU, Chau Mahla(CMU), Talavli(TLZ), LC-28, IBH-27, Thuria(THUR), IBH-23, VikramgarhA lot(VMA), IBH-17, LuniRichha(LNR), IBH-10, Mehidpur Road(MEP), 3.9 KM  from RLK, Rohalkhurd(RLK), LC-3, IBH-1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
